--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679E111C-9C89-48F1-9217-66C044188657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76606B37-26F9-4ABF-9360-52F8F944A972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="131">
   <si>
     <t>Original</t>
   </si>
@@ -418,12 +418,6 @@
   </si>
   <si>
     <t>HNN</t>
-  </si>
-  <si>
-    <t>Nok</t>
-  </si>
-  <si>
-    <t>467059531c111138</t>
   </si>
   <si>
     <t>HNN Result</t>
@@ -485,7 +479,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -508,11 +502,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,6 +555,15 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -827,7 +867,7 @@
         <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,14 +887,10 @@
       <c r="B3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -866,14 +902,10 @@
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>128</v>
-      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
       <c r="F4" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -888,7 +920,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="F5" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -1064,78 +1096,103 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B035164-966C-4B99-9EC3-82759FDF3491}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1143,270 +1200,343 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="10"/>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>99</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>106</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>109</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>110</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>112</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>113</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1415,270 +1545,343 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>99</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>101</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>106</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>108</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>109</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>110</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>112</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>113</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>114</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1687,15 +1890,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1705,19 +1910,27 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1727,8 +1940,10 @@
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -1738,8 +1953,10 @@
       <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -1749,8 +1966,10 @@
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1760,19 +1979,27 @@
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
@@ -1782,8 +2009,10 @@
       <c r="C9" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
@@ -1793,8 +2022,10 @@
       <c r="C10" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
@@ -1804,8 +2035,14 @@
       <c r="C11" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C8:E8"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1814,110 +2051,143 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>124</v>
       </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76606B37-26F9-4ABF-9360-52F8F944A972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951A7F2B-6B73-47B0-A756-5B558815399B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
@@ -22,22 +22,33 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$2:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$2:$D$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ParkDatabase!$A$1:$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="129">
   <si>
     <t>Original</t>
   </si>
@@ -423,13 +434,7 @@
     <t>HNN Result</t>
   </si>
   <si>
-    <t>1 Entrada com 128 = Underfitting</t>
-  </si>
-  <si>
-    <t>+ 3 Entradas com 128 = Overfitting</t>
-  </si>
-  <si>
-    <t>2-3 Entradas com 128 = Ok</t>
+    <t>e6g059131c111518</t>
   </si>
 </sst>
 </file>
@@ -846,17 +851,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A326E2B2-76FB-47EE-8B9A-ECDEE071B7A7}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
@@ -870,7 +874,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -880,160 +884,215 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>IF(C3=$B$2,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="F4" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <f>IF(C4=$B$2,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="F5" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f t="shared" ref="D5:D21" si="0">IF(C5=$B$2,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
@@ -1042,8 +1101,13 @@
       <c r="B17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
@@ -1052,8 +1116,13 @@
       <c r="B18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -1062,8 +1131,13 @@
       <c r="B19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
@@ -1072,8 +1146,13 @@
       <c r="B20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
@@ -1082,13 +1161,19 @@
       <c r="B21" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1101,8 +1186,8 @@
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1136,8 +1221,13 @@
       <c r="B3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>IF(C3=$B$2,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -1146,8 +1236,13 @@
       <c r="B4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <f t="shared" ref="D4:D8" si="0">IF(C4=$B$2,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1156,8 +1251,13 @@
       <c r="B5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1166,8 +1266,13 @@
       <c r="B6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1176,8 +1281,13 @@
       <c r="B7" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1186,8 +1296,13 @@
       <c r="B8" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1205,33 +1320,33 @@
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1240,8 +1355,13 @@
       <c r="B3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -1250,8 +1370,13 @@
       <c r="B4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1260,8 +1385,13 @@
       <c r="B5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1270,8 +1400,13 @@
       <c r="B6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="5" t="str">
+        <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1280,8 +1415,13 @@
       <c r="B7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1290,8 +1430,13 @@
       <c r="B8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1300,8 +1445,13 @@
       <c r="B9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1310,8 +1460,13 @@
       <c r="B10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="5" t="str">
+        <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1320,8 +1475,13 @@
       <c r="B11" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="5" t="str">
+        <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1330,8 +1490,13 @@
       <c r="B12" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="5" t="str">
+        <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1340,8 +1505,13 @@
       <c r="B13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="5" t="str">
+        <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1350,8 +1520,13 @@
       <c r="B14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="5" t="str">
+        <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1360,8 +1535,13 @@
       <c r="B15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="5" t="str">
+        <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1370,8 +1550,13 @@
       <c r="B16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="5" t="str">
+        <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1380,8 +1565,13 @@
       <c r="B17" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="5" t="str">
+        <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1390,8 +1580,13 @@
       <c r="B18" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="5" t="str">
+        <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1400,8 +1595,13 @@
       <c r="B19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="5" t="str">
+        <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1410,8 +1610,13 @@
       <c r="B20" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="5" t="str">
+        <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -1420,8 +1625,13 @@
       <c r="B21" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="5" t="str">
+        <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -1430,8 +1640,13 @@
       <c r="B22" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="5" t="str">
+        <f>IF(C22=$B$1,"Verdadeiro","Falso")</f>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1440,8 +1655,13 @@
       <c r="B23" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="5" t="str">
+        <f>IF(C23=$B$1,"Verdadeiro","Falso")</f>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1450,8 +1670,13 @@
       <c r="B24" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="5" t="str">
+        <f>IF(C24=$B$1,"Verdadeiro","Falso")</f>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1460,8 +1685,13 @@
       <c r="B25" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="5" t="str">
+        <f>IF(C25=$B$1,"Verdadeiro","Falso")</f>
+        <v>Falso</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1470,8 +1700,13 @@
       <c r="B26" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="5" t="str">
+        <f>IF(C26=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1480,8 +1715,13 @@
       <c r="B27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="5" t="str">
+        <f>IF(C27=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -1490,8 +1730,13 @@
       <c r="B28" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="5" t="str">
+        <f>IF(C28=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1500,8 +1745,13 @@
       <c r="B29" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="5" t="str">
+        <f>IF(C29=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1510,8 +1760,13 @@
       <c r="B30" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="5" t="str">
+        <f>IF(C30=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1520,8 +1775,13 @@
       <c r="B31" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="5" t="str">
+        <f>IF(C31=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1530,12 +1790,22 @@
       <c r="B32" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="5" t="str">
+        <f>IF(C32=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:D32" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D32">
+      <sortCondition ref="A2:A32"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1550,33 +1820,33 @@
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1585,8 +1855,13 @@
       <c r="B3" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -1595,8 +1870,13 @@
       <c r="B4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <f t="shared" ref="D4:D32" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1605,8 +1885,13 @@
       <c r="B5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1615,8 +1900,13 @@
       <c r="B6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1625,8 +1915,13 @@
       <c r="B7" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1635,8 +1930,13 @@
       <c r="B8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1645,8 +1945,13 @@
       <c r="B9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1655,8 +1960,13 @@
       <c r="B10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1665,8 +1975,13 @@
       <c r="B11" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1675,8 +1990,13 @@
       <c r="B12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1685,8 +2005,13 @@
       <c r="B13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1695,8 +2020,13 @@
       <c r="B14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1705,8 +2035,13 @@
       <c r="B15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1715,8 +2050,13 @@
       <c r="B16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1725,8 +2065,13 @@
       <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1735,8 +2080,13 @@
       <c r="B18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1745,8 +2095,13 @@
       <c r="B19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1755,8 +2110,13 @@
       <c r="B20" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -1765,8 +2125,13 @@
       <c r="B21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -1775,8 +2140,13 @@
       <c r="B22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1785,8 +2155,13 @@
       <c r="B23" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1795,8 +2170,13 @@
       <c r="B24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1805,8 +2185,13 @@
       <c r="B25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1815,8 +2200,13 @@
       <c r="B26" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1825,8 +2215,13 @@
       <c r="B27" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -1835,8 +2230,13 @@
       <c r="B28" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1845,8 +2245,13 @@
       <c r="B29" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1855,8 +2260,13 @@
       <c r="B30" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1865,8 +2275,13 @@
       <c r="B31" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1875,12 +2290,18 @@
       <c r="B32" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:D32" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}"/>
   <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951A7F2B-6B73-47B0-A756-5B558815399B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43507F7-0673-47C9-A60A-DD85FF6801E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,9 +21,9 @@
     <sheet name="ParkDatabase" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$2:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$2:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$2:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ParkDatabase!$A$1:$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
   </definedNames>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="161">
   <si>
     <t>Original</t>
   </si>
@@ -435,6 +435,102 @@
   </si>
   <si>
     <t>e6g059131c111518</t>
+  </si>
+  <si>
+    <t>Hamming Distance</t>
+  </si>
+  <si>
+    <t>Washington Database</t>
+  </si>
+  <si>
+    <t>Alternative (1)</t>
+  </si>
+  <si>
+    <t>Alternative (2)</t>
+  </si>
+  <si>
+    <t>Alternative (3)</t>
+  </si>
+  <si>
+    <t>Alternative (4)</t>
+  </si>
+  <si>
+    <t>Alternative (5)</t>
+  </si>
+  <si>
+    <t>Alternative (6)</t>
+  </si>
+  <si>
+    <t>Alternative (7)</t>
+  </si>
+  <si>
+    <t>Alternative (8)</t>
+  </si>
+  <si>
+    <t>Alternative (9)</t>
+  </si>
+  <si>
+    <t>Alternative (10)</t>
+  </si>
+  <si>
+    <t>Alternative (11)</t>
+  </si>
+  <si>
+    <t>Alternative (12)</t>
+  </si>
+  <si>
+    <t>Alternative (13)</t>
+  </si>
+  <si>
+    <t>Alternative (14)</t>
+  </si>
+  <si>
+    <t>Alternative (15)</t>
+  </si>
+  <si>
+    <t>Alternative (16)</t>
+  </si>
+  <si>
+    <t>Alternative (17)</t>
+  </si>
+  <si>
+    <t>Alternative (18)</t>
+  </si>
+  <si>
+    <t>Alternative (19)</t>
+  </si>
+  <si>
+    <t>Alternative (20)</t>
+  </si>
+  <si>
+    <t>Alternative (21)</t>
+  </si>
+  <si>
+    <t>Alternative (22)</t>
+  </si>
+  <si>
+    <t>Alternative (23)</t>
+  </si>
+  <si>
+    <t>Alternative (24)</t>
+  </si>
+  <si>
+    <t>Alternative (25)</t>
+  </si>
+  <si>
+    <t>Alternative (26)</t>
+  </si>
+  <si>
+    <t>Alternative (27)</t>
+  </si>
+  <si>
+    <t>Alternative (28)</t>
+  </si>
+  <si>
+    <t>Alternative (29)</t>
+  </si>
+  <si>
+    <t>Alternative (30)</t>
   </si>
 </sst>
 </file>
@@ -464,7 +560,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,8 +579,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -544,11 +646,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -569,6 +691,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -851,40 +993,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A326E2B2-76FB-47EE-8B9A-ECDEE071B7A7}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -895,11 +1042,14 @@
         <v>25</v>
       </c>
       <c r="D3" s="5" t="str">
-        <f>IF(C3=$B$2,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E3" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
@@ -910,11 +1060,14 @@
         <v>25</v>
       </c>
       <c r="D4" s="5" t="str">
-        <f>IF(C4=$B$2,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
@@ -925,11 +1078,14 @@
         <v>25</v>
       </c>
       <c r="D5" s="5" t="str">
-        <f t="shared" ref="D5:D21" si="0">IF(C5=$B$2,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E5" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
@@ -940,11 +1096,14 @@
         <v>25</v>
       </c>
       <c r="D6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E6" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>31</v>
       </c>
@@ -955,11 +1114,14 @@
         <v>25</v>
       </c>
       <c r="D7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>32</v>
       </c>
@@ -970,11 +1132,14 @@
         <v>25</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
@@ -985,11 +1150,14 @@
         <v>25</v>
       </c>
       <c r="D9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E9" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>34</v>
       </c>
@@ -1000,11 +1168,14 @@
         <v>25</v>
       </c>
       <c r="D10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>35</v>
       </c>
@@ -1015,11 +1186,14 @@
         <v>25</v>
       </c>
       <c r="D11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E11" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>37</v>
       </c>
@@ -1030,11 +1204,14 @@
         <v>25</v>
       </c>
       <c r="D12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E12" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
@@ -1045,11 +1222,14 @@
         <v>25</v>
       </c>
       <c r="D13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
@@ -1060,11 +1240,14 @@
         <v>25</v>
       </c>
       <c r="D14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
@@ -1075,11 +1258,14 @@
         <v>25</v>
       </c>
       <c r="D15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
@@ -1090,11 +1276,14 @@
         <v>25</v>
       </c>
       <c r="D16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E16" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
@@ -1105,11 +1294,14 @@
         <v>25</v>
       </c>
       <c r="D17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E17" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>45</v>
       </c>
@@ -1120,26 +1312,32 @@
         <v>25</v>
       </c>
       <c r="D18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+        <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E18" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="5" t="str">
-        <f t="shared" si="0"/>
+      <c r="D19" s="13" t="str">
+        <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>49</v>
       </c>
@@ -1150,11 +1348,14 @@
         <v>25</v>
       </c>
       <c r="D20" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E20" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>50</v>
       </c>
@@ -1165,13 +1366,16 @@
         <v>25</v>
       </c>
       <c r="D21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
+        <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E21" s="16">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1181,18 +1385,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B035164-966C-4B99-9EC3-82759FDF3491}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>23</v>
@@ -1203,18 +1408,22 @@
       <c r="D1" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>54</v>
       </c>
@@ -1228,8 +1437,11 @@
         <f>IF(C3=$B$2,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>56</v>
       </c>
@@ -1243,38 +1455,47 @@
         <f t="shared" ref="D4:D8" si="0">IF(C4=$B$2,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="E4" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="5" t="str">
+      <c r="D5" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="E5" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="5" t="str">
+      <c r="D6" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>62</v>
       </c>
@@ -1288,8 +1509,11 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>64</v>
       </c>
@@ -1303,10 +1527,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
+      <c r="E8" s="14">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1315,26 +1542,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -1347,10 +1576,13 @@
       <c r="D2" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>79</v>
@@ -1362,10 +1594,13 @@
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>80</v>
@@ -1377,10 +1612,13 @@
         <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>81</v>
@@ -1392,10 +1630,13 @@
         <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>81</v>
@@ -1407,10 +1648,13 @@
         <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>78</v>
@@ -1422,10 +1666,13 @@
         <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>82</v>
@@ -1437,10 +1684,13 @@
         <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>79</v>
@@ -1452,10 +1702,13 @@
         <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>82</v>
@@ -1467,10 +1720,13 @@
         <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>78</v>
@@ -1482,10 +1738,13 @@
         <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>83</v>
@@ -1497,10 +1756,13 @@
         <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>83</v>
@@ -1512,10 +1774,13 @@
         <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>79</v>
@@ -1527,10 +1792,13 @@
         <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>78</v>
@@ -1542,10 +1810,13 @@
         <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>84</v>
@@ -1557,10 +1828,13 @@
         <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>81</v>
@@ -1572,10 +1846,13 @@
         <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>81</v>
@@ -1587,115 +1864,139 @@
         <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="5" t="s">
+      <c r="E18" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="5" t="str">
+      <c r="D19" s="13" t="str">
         <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="E19" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="5" t="str">
+      <c r="D20" s="13" t="str">
         <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="E20" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D21" s="5" t="str">
+      <c r="D21" s="13" t="str">
         <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="E21" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="5" t="str">
+      <c r="D22" s="13" t="str">
         <f>IF(C22=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="5" t="s">
+      <c r="E22" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="5" t="str">
+      <c r="D23" s="13" t="str">
         <f>IF(C23=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="E23" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D24" s="5" t="str">
+      <c r="D24" s="13" t="str">
         <f>IF(C24=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="E24" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="5" t="str">
+      <c r="D25" s="13" t="str">
         <f>IF(C25=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>82</v>
@@ -1707,10 +2008,13 @@
         <f>IF(C26=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>82</v>
@@ -1722,10 +2026,13 @@
         <f>IF(C27=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>78</v>
@@ -1737,10 +2044,13 @@
         <f>IF(C28=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>78</v>
@@ -1752,10 +2062,13 @@
         <f>IF(C29=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>81</v>
@@ -1767,10 +2080,13 @@
         <f>IF(C30=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>83</v>
@@ -1782,10 +2098,13 @@
         <f>IF(C31=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>82</v>
@@ -1797,15 +2116,18 @@
         <f>IF(C32=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
+      <c r="E32" s="14">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D32" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D32">
-      <sortCondition ref="A2:A32"/>
+  <autoFilter ref="A2:E2" xr:uid="{B4A2C3A5-6967-4B84-966A-7CAAAA1E890F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E32">
+      <sortCondition ref="A2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1815,26 +2137,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
@@ -1847,8 +2171,11 @@
       <c r="D2" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
@@ -1862,8 +2189,9 @@
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="14"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>86</v>
       </c>
@@ -1877,8 +2205,9 @@
         <f t="shared" ref="D4:D32" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>87</v>
       </c>
@@ -1892,8 +2221,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>88</v>
       </c>
@@ -1907,8 +2237,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>89</v>
       </c>
@@ -1922,8 +2253,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>90</v>
       </c>
@@ -1937,8 +2269,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>91</v>
       </c>
@@ -1952,8 +2285,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="14"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>92</v>
       </c>
@@ -1967,8 +2301,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="14"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
@@ -1982,8 +2317,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
@@ -1997,8 +2333,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="14"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>95</v>
       </c>
@@ -2012,8 +2349,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>96</v>
       </c>
@@ -2027,8 +2365,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>97</v>
       </c>
@@ -2042,8 +2381,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>98</v>
       </c>
@@ -2057,8 +2397,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>99</v>
       </c>
@@ -2072,8 +2413,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>100</v>
       </c>
@@ -2087,8 +2429,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>101</v>
       </c>
@@ -2102,8 +2445,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>102</v>
       </c>
@@ -2117,8 +2461,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="14"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>103</v>
       </c>
@@ -2132,8 +2477,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>104</v>
       </c>
@@ -2147,8 +2493,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>105</v>
       </c>
@@ -2162,8 +2509,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>106</v>
       </c>
@@ -2177,8 +2525,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="14"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>107</v>
       </c>
@@ -2192,8 +2541,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="14"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>108</v>
       </c>
@@ -2207,8 +2557,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="14"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>109</v>
       </c>
@@ -2222,8 +2573,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="14"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>110</v>
       </c>
@@ -2237,8 +2589,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="14"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>111</v>
       </c>
@@ -2252,8 +2605,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="14"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>112</v>
       </c>
@@ -2267,8 +2621,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="14"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>113</v>
       </c>
@@ -2282,8 +2637,9 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="14"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>114</v>
       </c>
@@ -2297,11 +2653,12 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
+      <c r="E32" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:D32" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}"/>
   <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -8,23 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43507F7-0673-47C9-A60A-DD85FF6801E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA41E4A6-21B5-4B93-A94A-1098E7AC330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
     <sheet name="WashingtonDatabase" sheetId="3" r:id="rId2"/>
     <sheet name="PalaceDatabase" sheetId="6" r:id="rId3"/>
     <sheet name="MountainDatabase" sheetId="5" r:id="rId4"/>
-    <sheet name="DevicesDatabase" sheetId="1" r:id="rId5"/>
-    <sheet name="ParkDatabase" sheetId="7" r:id="rId6"/>
+    <sheet name="ParkDatabase" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$2:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$2:$D$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ParkDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ParkDatabase!$A$1:$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,77 +47,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="161">
-  <si>
-    <t>Original</t>
-  </si>
-  <si>
-    <t>Devices Database</t>
-  </si>
-  <si>
-    <t>Blackberry (1)</t>
-  </si>
-  <si>
-    <t>Nome da Imagem</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="119">
   <si>
     <t>D-Hash</t>
   </si>
   <si>
-    <t>d9d9d9d3d1d0d0f2</t>
-  </si>
-  <si>
-    <t>Altered 01</t>
-  </si>
-  <si>
-    <t>Altered 02</t>
-  </si>
-  <si>
-    <t>Altered 03</t>
-  </si>
-  <si>
-    <t>Canon (1)</t>
-  </si>
-  <si>
-    <t>dada52d35151f331</t>
-  </si>
-  <si>
-    <t>Iphone (1)</t>
-  </si>
-  <si>
-    <t>9999d193d0d0f0a1</t>
-  </si>
-  <si>
-    <t>Sony (1)</t>
-  </si>
-  <si>
-    <t>d9d9d2d1d0d0f321</t>
-  </si>
-  <si>
-    <t>Blackberry (2)</t>
-  </si>
-  <si>
-    <t>6870d947e4ed41e5</t>
-  </si>
-  <si>
-    <t>31f216c4ee6363a2</t>
-  </si>
-  <si>
-    <t>Canon (2)</t>
-  </si>
-  <si>
-    <t>68f1b3cdc44dc185</t>
-  </si>
-  <si>
-    <t>Iphone (2)</t>
-  </si>
-  <si>
-    <t>78b052c4c9434763</t>
-  </si>
-  <si>
-    <t>Sony (2)</t>
-  </si>
-  <si>
     <t>D.Hashing</t>
   </si>
   <si>
@@ -333,66 +266,6 @@
   </si>
   <si>
     <t>Alternative 10</t>
-  </si>
-  <si>
-    <t>Alternative 11</t>
-  </si>
-  <si>
-    <t>Alternative 12</t>
-  </si>
-  <si>
-    <t>Alternative 13</t>
-  </si>
-  <si>
-    <t>Alternative 14</t>
-  </si>
-  <si>
-    <t>Alternative 15</t>
-  </si>
-  <si>
-    <t>Alternative 16</t>
-  </si>
-  <si>
-    <t>Alternative 17</t>
-  </si>
-  <si>
-    <t>Alternative 18</t>
-  </si>
-  <si>
-    <t>Alternative 19</t>
-  </si>
-  <si>
-    <t>Alternative 20</t>
-  </si>
-  <si>
-    <t>Alternative 21</t>
-  </si>
-  <si>
-    <t>Alternative 22</t>
-  </si>
-  <si>
-    <t>Alternative 23</t>
-  </si>
-  <si>
-    <t>Alternative 24</t>
-  </si>
-  <si>
-    <t>Alternative 25</t>
-  </si>
-  <si>
-    <t>Alternative 26</t>
-  </si>
-  <si>
-    <t>Alternative 27</t>
-  </si>
-  <si>
-    <t>Alternative 28</t>
-  </si>
-  <si>
-    <t>Alternative 29</t>
-  </si>
-  <si>
-    <t>Alternative 30</t>
   </si>
   <si>
     <t>eecede9d3e7cb6b6</t>
@@ -1005,10 +878,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -1016,30 +889,30 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
@@ -1051,13 +924,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="str">
         <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
@@ -1069,13 +942,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5" t="str">
         <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
@@ -1087,13 +960,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="str">
         <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
@@ -1105,13 +978,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D7" s="5" t="str">
         <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
@@ -1123,13 +996,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="str">
         <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
@@ -1141,13 +1014,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D9" s="5" t="str">
         <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
@@ -1159,13 +1032,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="str">
         <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
@@ -1177,13 +1050,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="str">
         <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
@@ -1195,13 +1068,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="str">
         <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
@@ -1213,13 +1086,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="str">
         <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
@@ -1231,13 +1104,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="str">
         <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
@@ -1249,13 +1122,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5" t="str">
         <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
@@ -1267,13 +1140,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D16" s="5" t="str">
         <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
@@ -1285,13 +1158,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="str">
         <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
@@ -1303,13 +1176,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D18" s="5" t="str">
         <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
@@ -1321,13 +1194,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
@@ -1339,13 +1212,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D20" s="5" t="str">
         <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
@@ -1357,13 +1230,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="str">
         <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
@@ -1397,27 +1270,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -1425,13 +1298,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>IF(C3=$B$2,"Verdadeiro","Falso")</f>
@@ -1443,13 +1316,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="str">
         <f t="shared" ref="D4:D8" si="0">IF(C4=$B$2,"Verdadeiro","Falso")</f>
@@ -1461,13 +1334,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D5" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1479,13 +1352,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D6" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1497,13 +1370,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -1515,13 +1388,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -1554,10 +1427,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -1565,30 +1438,30 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
@@ -1600,13 +1473,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D4" s="5" t="str">
         <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
@@ -1618,13 +1491,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D5" s="5" t="str">
         <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
@@ -1636,13 +1509,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D6" s="5" t="str">
         <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
@@ -1654,13 +1527,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D7" s="5" t="str">
         <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
@@ -1672,13 +1545,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D8" s="5" t="str">
         <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
@@ -1690,13 +1563,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D9" s="5" t="str">
         <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
@@ -1708,13 +1581,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D10" s="5" t="str">
         <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
@@ -1726,13 +1599,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5" t="str">
         <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
@@ -1744,13 +1617,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D12" s="5" t="str">
         <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
@@ -1762,13 +1635,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5" t="str">
         <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
@@ -1780,13 +1653,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5" t="str">
         <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
@@ -1798,13 +1671,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5" t="str">
         <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
@@ -1816,13 +1689,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5" t="str">
         <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
@@ -1834,13 +1707,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D17" s="5" t="str">
         <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
@@ -1852,13 +1725,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D18" s="5" t="str">
         <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
@@ -1870,13 +1743,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
@@ -1888,13 +1761,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
@@ -1906,13 +1779,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
@@ -1924,13 +1797,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>IF(C22=$B$1,"Verdadeiro","Falso")</f>
@@ -1942,13 +1815,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>IF(C23=$B$1,"Verdadeiro","Falso")</f>
@@ -1960,13 +1833,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D24" s="13" t="str">
         <f>IF(C24=$B$1,"Verdadeiro","Falso")</f>
@@ -1978,13 +1851,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D25" s="13" t="str">
         <f>IF(C25=$B$1,"Verdadeiro","Falso")</f>
@@ -1996,13 +1869,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D26" s="5" t="str">
         <f>IF(C26=$B$1,"Verdadeiro","Falso")</f>
@@ -2014,13 +1887,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D27" s="5" t="str">
         <f>IF(C27=$B$1,"Verdadeiro","Falso")</f>
@@ -2032,13 +1905,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D28" s="5" t="str">
         <f>IF(C28=$B$1,"Verdadeiro","Falso")</f>
@@ -2050,13 +1923,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D29" s="5" t="str">
         <f>IF(C29=$B$1,"Verdadeiro","Falso")</f>
@@ -2068,13 +1941,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D30" s="5" t="str">
         <f>IF(C30=$B$1,"Verdadeiro","Falso")</f>
@@ -2086,13 +1959,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D31" s="5" t="str">
         <f>IF(C31=$B$1,"Verdadeiro","Falso")</f>
@@ -2104,13 +1977,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D32" s="5" t="str">
         <f>IF(C32=$B$1,"Verdadeiro","Falso")</f>
@@ -2149,10 +2022,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -2160,500 +2033,560 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="str">
         <f t="shared" ref="D4:D32" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D15" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D16" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D17" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D19" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D20" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E20" s="14"/>
+      <c r="E20" s="14">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D21" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="14">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="14">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D23" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="14">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D24" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E24" s="14"/>
+      <c r="E24" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D25" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E25" s="14"/>
+      <c r="E25" s="14">
+        <v>5</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D26" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E26" s="14"/>
+      <c r="E26" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D27" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D29" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D30" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D31" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D32" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="14">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D32" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}"/>
@@ -2667,167 +2600,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C8:E8"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2840,124 +2612,124 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>

--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA41E4A6-21B5-4B93-A94A-1098E7AC330B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DAF720-350D-4309-A188-DAD44470B846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$2:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$2:$D$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ParkDatabase!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ParkDatabase!$A$2:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="109">
   <si>
     <t>D-Hash</t>
   </si>
@@ -236,36 +236,6 @@
   </si>
   <si>
     <t>e6ce8e8918149694</t>
-  </si>
-  <si>
-    <t>Alternative 01</t>
-  </si>
-  <si>
-    <t>Alternative 02</t>
-  </si>
-  <si>
-    <t>Alternative 03</t>
-  </si>
-  <si>
-    <t>Alternative 04</t>
-  </si>
-  <si>
-    <t>Alternative 05</t>
-  </si>
-  <si>
-    <t>Alternative 06</t>
-  </si>
-  <si>
-    <t>Alternative 07</t>
-  </si>
-  <si>
-    <t>Alternative 08</t>
-  </si>
-  <si>
-    <t>Alternative 09</t>
-  </si>
-  <si>
-    <t>Alternative 10</t>
   </si>
   <si>
     <t>eecede9d3e7cb6b6</t>
@@ -543,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -567,6 +537,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -585,6 +558,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -895,13 +871,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -918,7 +894,7 @@
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="17">
         <v>2</v>
       </c>
     </row>
@@ -936,7 +912,7 @@
         <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="17">
         <v>0</v>
       </c>
     </row>
@@ -954,7 +930,7 @@
         <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="17">
         <v>0</v>
       </c>
     </row>
@@ -972,7 +948,7 @@
         <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="17">
         <v>0</v>
       </c>
     </row>
@@ -990,7 +966,7 @@
         <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1008,7 +984,7 @@
         <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1026,7 +1002,7 @@
         <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1044,7 +1020,7 @@
         <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1062,7 +1038,7 @@
         <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="17">
         <v>2</v>
       </c>
     </row>
@@ -1080,7 +1056,7 @@
         <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="17">
         <v>8</v>
       </c>
     </row>
@@ -1098,7 +1074,7 @@
         <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1116,7 +1092,7 @@
         <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1134,7 +1110,7 @@
         <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1152,7 +1128,7 @@
         <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1170,7 +1146,7 @@
         <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="17">
         <v>1</v>
       </c>
     </row>
@@ -1188,7 +1164,7 @@
         <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="17">
         <v>5</v>
       </c>
     </row>
@@ -1196,17 +1172,17 @@
       <c r="A19" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="13" t="str">
+      <c r="C19" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="14" t="str">
         <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="18">
         <v>14</v>
       </c>
     </row>
@@ -1224,7 +1200,7 @@
         <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1242,7 +1218,7 @@
         <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="17">
         <v>5</v>
       </c>
     </row>
@@ -1270,19 +1246,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1310,7 +1286,7 @@
         <f>IF(C3=$B$2,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="15">
         <v>7</v>
       </c>
     </row>
@@ -1328,43 +1304,43 @@
         <f t="shared" ref="D4:D8" si="0">IF(C4=$B$2,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="13" t="str">
+      <c r="C5" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="13" t="str">
+      <c r="C6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="16">
         <v>12</v>
       </c>
     </row>
@@ -1382,7 +1358,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1400,7 +1376,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="15">
         <v>3</v>
       </c>
     </row>
@@ -1429,12 +1405,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1444,18 +1420,18 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>57</v>
@@ -1467,13 +1443,13 @@
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>58</v>
@@ -1485,13 +1461,13 @@
         <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>59</v>
@@ -1503,13 +1479,13 @@
         <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>59</v>
@@ -1521,13 +1497,13 @@
         <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>56</v>
@@ -1539,13 +1515,13 @@
         <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>60</v>
@@ -1557,13 +1533,13 @@
         <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>57</v>
@@ -1575,13 +1551,13 @@
         <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>60</v>
@@ -1593,13 +1569,13 @@
         <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>56</v>
@@ -1611,13 +1587,13 @@
         <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>61</v>
@@ -1629,13 +1605,13 @@
         <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>61</v>
@@ -1647,13 +1623,13 @@
         <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>57</v>
@@ -1665,13 +1641,13 @@
         <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>56</v>
@@ -1683,13 +1659,13 @@
         <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>62</v>
@@ -1701,13 +1677,13 @@
         <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>59</v>
@@ -1719,13 +1695,13 @@
         <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>59</v>
@@ -1737,139 +1713,139 @@
         <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="13" t="str">
+      <c r="A19" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="14" t="str">
         <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="16">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="13" t="str">
+      <c r="A20" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="14" t="str">
         <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="16">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="13" t="str">
+      <c r="A21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="14" t="str">
         <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="16">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="13" t="str">
+      <c r="A22" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="14" t="str">
         <f>IF(C22=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="16">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="13" t="str">
+      <c r="D23" s="14" t="str">
         <f>IF(C23=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="16">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="13" t="str">
+      <c r="A24" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="14" t="str">
         <f>IF(C24=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="16">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="13" t="str">
+      <c r="A25" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="14" t="str">
         <f>IF(C25=$B$1,"Verdadeiro","Falso")</f>
         <v>Falso</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="16">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>60</v>
@@ -1881,13 +1857,13 @@
         <f>IF(C26=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>60</v>
@@ -1899,13 +1875,13 @@
         <f>IF(C27=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>56</v>
@@ -1917,13 +1893,13 @@
         <f>IF(C28=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>56</v>
@@ -1935,13 +1911,13 @@
         <f>IF(C29=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>59</v>
@@ -1953,13 +1929,13 @@
         <f>IF(C30=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>61</v>
@@ -1971,13 +1947,13 @@
         <f>IF(C31=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>60</v>
@@ -1989,7 +1965,7 @@
         <f>IF(C32=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="15">
         <v>1</v>
       </c>
     </row>
@@ -2024,12 +2000,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="B1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2039,18 +2015,18 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>47</v>
@@ -2062,13 +2038,13 @@
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>47</v>
@@ -2080,13 +2056,13 @@
         <f t="shared" ref="D4:D32" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>48</v>
@@ -2098,13 +2074,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>48</v>
@@ -2116,13 +2092,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>48</v>
@@ -2134,13 +2110,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>47</v>
@@ -2152,13 +2128,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>48</v>
@@ -2170,13 +2146,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>48</v>
@@ -2188,13 +2164,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>48</v>
@@ -2206,13 +2182,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>47</v>
@@ -2224,13 +2200,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>48</v>
@@ -2242,13 +2218,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>48</v>
@@ -2260,13 +2236,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>47</v>
@@ -2278,13 +2254,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>47</v>
@@ -2296,13 +2272,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>47</v>
@@ -2314,13 +2290,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>48</v>
@@ -2332,13 +2308,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>50</v>
@@ -2350,13 +2326,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>51</v>
@@ -2368,13 +2344,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>52</v>
@@ -2386,13 +2362,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>53</v>
@@ -2404,13 +2380,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>52</v>
@@ -2422,13 +2398,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>54</v>
@@ -2440,13 +2416,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>49</v>
@@ -2458,13 +2434,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>48</v>
@@ -2476,13 +2452,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>47</v>
@@ -2494,13 +2470,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>47</v>
@@ -2512,13 +2488,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>47</v>
@@ -2530,13 +2506,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>47</v>
@@ -2548,13 +2524,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>47</v>
@@ -2566,13 +2542,13 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>47</v>
@@ -2584,7 +2560,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="15">
         <v>1</v>
       </c>
     </row>
@@ -2601,142 +2577,235 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}">
-  <dimension ref="A1:D12"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E3" s="15">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <f t="shared" ref="D4:D12" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E8" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="B9" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E9" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E10" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E11" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E12" s="15">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:E12" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="4659d98bcbcb9e39"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DAF720-350D-4309-A188-DAD44470B846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD2F3E0-B9E2-4D01-9646-B790DA451F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="PalaceDatabase" sheetId="6" r:id="rId3"/>
     <sheet name="MountainDatabase" sheetId="5" r:id="rId4"/>
     <sheet name="ParkDatabase" sheetId="7" r:id="rId5"/>
+    <sheet name="Results" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$2:$A$2</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="126">
   <si>
     <t>D-Hash</t>
   </si>
@@ -374,13 +375,67 @@
   </si>
   <si>
     <t>Alternative (30)</t>
+  </si>
+  <si>
+    <t>Total de Imagens Utilizadas</t>
+  </si>
+  <si>
+    <t>Treinamento</t>
+  </si>
+  <si>
+    <t>Imagens Alteradas</t>
+  </si>
+  <si>
+    <t>&gt; 8</t>
+  </si>
+  <si>
+    <t>Hamming Distance Limiar</t>
+  </si>
+  <si>
+    <t>Hopfield - Acerto</t>
+  </si>
+  <si>
+    <t>Hopfield - Erro</t>
+  </si>
+  <si>
+    <t>Acurácia</t>
+  </si>
+  <si>
+    <t>Acerto</t>
+  </si>
+  <si>
+    <t>Erro</t>
+  </si>
+  <si>
+    <t>Lenna</t>
+  </si>
+  <si>
+    <t>Montanha</t>
+  </si>
+  <si>
+    <t>Total de Imagens</t>
+  </si>
+  <si>
+    <t>Palácio</t>
+  </si>
+  <si>
+    <t>Parque</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,8 +457,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,6 +502,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -510,10 +596,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,18 +613,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -553,18 +630,47 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Bom" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Ruim" xfId="3" builtinId="27"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -856,12 +962,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -891,10 +997,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="5" t="str">
-        <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E3" s="17">
+        <f t="shared" ref="D3:D21" si="0">IF(C3=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E3" s="13">
         <v>2</v>
       </c>
     </row>
@@ -909,10 +1015,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="5" t="str">
-        <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E4" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E4" s="13">
         <v>0</v>
       </c>
     </row>
@@ -927,10 +1033,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="str">
-        <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E5" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E5" s="13">
         <v>0</v>
       </c>
     </row>
@@ -945,10 +1051,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="5" t="str">
-        <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E6" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E6" s="13">
         <v>0</v>
       </c>
     </row>
@@ -963,10 +1069,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="str">
-        <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E7" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E7" s="13">
         <v>0</v>
       </c>
     </row>
@@ -981,10 +1087,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E8" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E8" s="13">
         <v>0</v>
       </c>
     </row>
@@ -999,10 +1105,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="5" t="str">
-        <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E9" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E9" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1017,10 +1123,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="5" t="str">
-        <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E10" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E10" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1035,10 +1141,10 @@
         <v>3</v>
       </c>
       <c r="D11" s="5" t="str">
-        <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E11" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E11" s="13">
         <v>2</v>
       </c>
     </row>
@@ -1053,10 +1159,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="5" t="str">
-        <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E12" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E12" s="13">
         <v>8</v>
       </c>
     </row>
@@ -1071,10 +1177,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="5" t="str">
-        <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E13" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E13" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1089,10 +1195,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="5" t="str">
-        <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E14" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E14" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1107,10 +1213,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="5" t="str">
-        <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E15" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E15" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1125,10 +1231,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="5" t="str">
-        <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E16" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E16" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1143,10 +1249,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="5" t="str">
-        <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E17" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E17" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1161,28 +1267,28 @@
         <v>3</v>
       </c>
       <c r="D18" s="5" t="str">
-        <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E18" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E18" s="13">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="14" t="str">
-        <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D19" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="14">
         <v>14</v>
       </c>
     </row>
@@ -1197,10 +1303,10 @@
         <v>3</v>
       </c>
       <c r="D20" s="5" t="str">
-        <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E20" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E20" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1215,10 +1321,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="5" t="str">
-        <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E21" s="17">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E21" s="13">
         <v>5</v>
       </c>
     </row>
@@ -1265,12 +1371,12 @@
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="11"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1286,7 +1392,7 @@
         <f>IF(C3=$B$2,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="11">
         <v>7</v>
       </c>
     </row>
@@ -1304,43 +1410,43 @@
         <f t="shared" ref="D4:D8" si="0">IF(C4=$B$2,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="11">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="14" t="str">
+      <c r="D5" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="14" t="str">
+      <c r="D6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="12">
         <v>12</v>
       </c>
     </row>
@@ -1358,7 +1464,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>5</v>
       </c>
     </row>
@@ -1376,7 +1482,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1440,10 +1546,10 @@
         <v>56</v>
       </c>
       <c r="D3" s="5" t="str">
-        <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E3" s="15">
+        <f t="shared" ref="D3:D32" si="0">IF(C3=$B$1,"Verdadeiro","Falso")</f>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E3" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1458,10 +1564,10 @@
         <v>56</v>
       </c>
       <c r="D4" s="5" t="str">
-        <f>IF(C4=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E4" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E4" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1476,10 +1582,10 @@
         <v>56</v>
       </c>
       <c r="D5" s="5" t="str">
-        <f>IF(C5=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E5" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E5" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1494,10 +1600,10 @@
         <v>56</v>
       </c>
       <c r="D6" s="5" t="str">
-        <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E6" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E6" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1512,10 +1618,10 @@
         <v>56</v>
       </c>
       <c r="D7" s="5" t="str">
-        <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E7" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E7" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1530,10 +1636,10 @@
         <v>56</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E8" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E8" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1548,10 +1654,10 @@
         <v>56</v>
       </c>
       <c r="D9" s="5" t="str">
-        <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E9" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E9" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1566,10 +1672,10 @@
         <v>56</v>
       </c>
       <c r="D10" s="5" t="str">
-        <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E10" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E10" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1584,10 +1690,10 @@
         <v>56</v>
       </c>
       <c r="D11" s="5" t="str">
-        <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E11" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E11" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1602,10 +1708,10 @@
         <v>56</v>
       </c>
       <c r="D12" s="5" t="str">
-        <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E12" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E12" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1620,10 +1726,10 @@
         <v>56</v>
       </c>
       <c r="D13" s="5" t="str">
-        <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E13" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E13" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1638,10 +1744,10 @@
         <v>56</v>
       </c>
       <c r="D14" s="5" t="str">
-        <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E14" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E14" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1656,10 +1762,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="5" t="str">
-        <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E15" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E15" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1674,10 +1780,10 @@
         <v>56</v>
       </c>
       <c r="D16" s="5" t="str">
-        <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E16" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E16" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1692,10 +1798,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="5" t="str">
-        <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E17" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E17" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1710,136 +1816,136 @@
         <v>56</v>
       </c>
       <c r="D18" s="5" t="str">
-        <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E18" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E18" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="14" t="str">
-        <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D19" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="12">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="14" t="str">
-        <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D20" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="12">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="14" t="str">
-        <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D21" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="12">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="14" t="str">
-        <f>IF(C22=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D22" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="12">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="14" t="str">
-        <f>IF(C23=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D23" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="12">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="14" t="str">
-        <f>IF(C24=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D24" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="12">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="14" t="str">
-        <f>IF(C25=$B$1,"Verdadeiro","Falso")</f>
+      <c r="D25" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>Falso</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="12">
         <v>9</v>
       </c>
     </row>
@@ -1854,10 +1960,10 @@
         <v>56</v>
       </c>
       <c r="D26" s="5" t="str">
-        <f>IF(C26=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E26" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E26" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1872,10 +1978,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="5" t="str">
-        <f>IF(C27=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E27" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E27" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1890,10 +1996,10 @@
         <v>56</v>
       </c>
       <c r="D28" s="5" t="str">
-        <f>IF(C28=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E28" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E28" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1908,10 +2014,10 @@
         <v>56</v>
       </c>
       <c r="D29" s="5" t="str">
-        <f>IF(C29=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E29" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E29" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1926,10 +2032,10 @@
         <v>56</v>
       </c>
       <c r="D30" s="5" t="str">
-        <f>IF(C30=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E30" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E30" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1944,10 +2050,10 @@
         <v>56</v>
       </c>
       <c r="D31" s="5" t="str">
-        <f>IF(C31=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E31" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E31" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1962,10 +2068,10 @@
         <v>56</v>
       </c>
       <c r="D32" s="5" t="str">
-        <f>IF(C32=$B$1,"Verdadeiro","Falso")</f>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E32" s="15">
+        <f t="shared" si="0"/>
+        <v>Verdadeiro</v>
+      </c>
+      <c r="E32" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2038,7 +2144,7 @@
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2056,7 +2162,7 @@
         <f t="shared" ref="D4:D32" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2074,7 +2180,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2092,7 +2198,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2110,7 +2216,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2128,7 +2234,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2146,7 +2252,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2164,7 +2270,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2182,7 +2288,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2200,7 +2306,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2218,7 +2324,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2236,7 +2342,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2254,7 +2360,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2272,7 +2378,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2290,7 +2396,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2308,7 +2414,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2326,7 +2432,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2344,7 +2450,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2362,7 +2468,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2380,7 +2486,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2398,7 +2504,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2416,7 +2522,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2434,7 +2540,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2452,7 +2558,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2470,7 +2576,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2488,7 +2594,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2506,7 +2612,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2524,7 +2630,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2542,7 +2648,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2560,7 +2666,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2577,7 +2683,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2585,19 +2690,19 @@
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2612,11 +2717,11 @@
       <c r="D2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>79</v>
       </c>
@@ -2630,11 +2735,11 @@
         <f>IF(C3=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>80</v>
       </c>
@@ -2648,11 +2753,11 @@
         <f t="shared" ref="D4:D12" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>81</v>
       </c>
@@ -2666,7 +2771,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2684,7 +2789,7 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2702,11 +2807,11 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>84</v>
       </c>
@@ -2720,11 +2825,11 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E8" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>85</v>
       </c>
@@ -2738,11 +2843,11 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E9" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>86</v>
       </c>
@@ -2756,11 +2861,11 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E10" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>87</v>
       </c>
@@ -2774,11 +2879,11 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E11" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>88</v>
       </c>
@@ -2792,22 +2897,190 @@
         <f t="shared" si="0"/>
         <v>Verdadeiro</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="11">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E12" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="4659d98bcbcb9e39"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:E12" xr:uid="{6DBCD1E4-A4CE-4DD2-A30A-CDCAA42489B3}"/>
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB04499-3846-46B9-A536-A8ACD3F24396}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="22">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="11">
+        <v>19</v>
+      </c>
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+      <c r="G2" s="11">
+        <f xml:space="preserve"> SUM(E2:F2)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="22">
+        <f xml:space="preserve"> SUM(G2:G6)</f>
+        <v>96</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="11">
+        <v>30</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <f t="shared" ref="G3:G10" si="0" xml:space="preserve"> SUM(E3:F3)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="D4" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="11">
+        <v>23</v>
+      </c>
+      <c r="F4" s="11">
+        <v>7</v>
+      </c>
+      <c r="G4" s="11">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="23"/>
+      <c r="B5" s="22"/>
+      <c r="D5" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="11">
+        <v>10</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="11">
+        <v>4</v>
+      </c>
+      <c r="F6" s="11">
+        <v>2</v>
+      </c>
+      <c r="G6" s="11">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="25">
+        <v>0.89600000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="24">
+        <v>0.104</v>
+      </c>
+      <c r="E8" s="5">
+        <f xml:space="preserve"> SUM(E2:E6)</f>
+        <v>86</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" ref="F8:G8" si="1" xml:space="preserve"> SUM(F2:F6)</f>
+        <v>10</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="26">
+        <f xml:space="preserve"> E8/G8</f>
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="F9" s="27">
+        <f xml:space="preserve"> F8/G8</f>
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="G9" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD2F3E0-B9E2-4D01-9646-B790DA451F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1B3B9D-CAC9-4EA5-AE19-68D2D463705B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$2:$A$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$2:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MountainDatabase!$A$2:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ParkDatabase!$A$2:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WashingtonDatabase!$A$1:$A$1</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="126">
   <si>
     <t>D-Hash</t>
   </si>
@@ -633,6 +633,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -651,20 +665,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bom" xfId="2" builtinId="26"/>
@@ -962,12 +962,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1371,12 +1371,12 @@
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1511,12 +1511,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2092,7 +2092,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -2106,12 +2106,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2159,7 +2159,7 @@
         <v>45</v>
       </c>
       <c r="D4" s="5" t="str">
-        <f t="shared" ref="D4:D32" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" ref="D4:D5" si="0">IF(C4=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E4" s="11">
@@ -2195,7 +2195,7 @@
         <v>45</v>
       </c>
       <c r="D6" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E6" s="11">
@@ -2207,17 +2207,17 @@
         <v>83</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E7" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2225,17 +2225,17 @@
         <v>84</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E8" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2249,7 +2249,7 @@
         <v>45</v>
       </c>
       <c r="D9" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E9" s="11">
@@ -2260,14 +2260,14 @@
       <c r="A10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E10" s="11">
@@ -2278,36 +2278,36 @@
       <c r="A11" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>48</v>
+      <c r="B11" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E11" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>47</v>
+      <c r="B12" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E12" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2321,7 +2321,7 @@
         <v>45</v>
       </c>
       <c r="D13" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E13" s="11">
@@ -2333,17 +2333,17 @@
         <v>90</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D14" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E14" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2357,7 +2357,7 @@
         <v>45</v>
       </c>
       <c r="D15" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E15" s="11">
@@ -2368,14 +2368,14 @@
       <c r="A16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E16" s="11">
@@ -2387,17 +2387,17 @@
         <v>93</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E17" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2405,17 +2405,17 @@
         <v>94</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E18" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2423,17 +2423,17 @@
         <v>95</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D19" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E19" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,13 +2441,13 @@
         <v>96</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D20" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E20" s="11">
@@ -2459,17 +2459,17 @@
         <v>97</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D21" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E21" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2477,17 +2477,17 @@
         <v>98</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D22" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C22=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E22" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2495,17 +2495,17 @@
         <v>99</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D23" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C23=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E23" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2513,17 +2513,17 @@
         <v>100</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D24" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C24=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E24" s="11">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2531,17 +2531,17 @@
         <v>101</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C25=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E25" s="11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2549,17 +2549,17 @@
         <v>102</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D26" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C26=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E26" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2573,7 +2573,7 @@
         <v>45</v>
       </c>
       <c r="D27" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C27=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E27" s="11">
@@ -2591,7 +2591,7 @@
         <v>45</v>
       </c>
       <c r="D28" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C28=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E28" s="11">
@@ -2609,7 +2609,7 @@
         <v>45</v>
       </c>
       <c r="D29" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C29=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E29" s="11">
@@ -2627,7 +2627,7 @@
         <v>45</v>
       </c>
       <c r="D30" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C30=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E30" s="11">
@@ -2645,33 +2645,15 @@
         <v>45</v>
       </c>
       <c r="D31" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(C31=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E31" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Verdadeiro</v>
-      </c>
-      <c r="E32" s="11">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D32" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}"/>
+  <autoFilter ref="A2:D31" xr:uid="{C435B1E9-7B1F-4BC3-9503-01F589155C74}"/>
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
@@ -2697,12 +2679,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2938,10 +2920,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="16">
         <v>5</v>
       </c>
       <c r="D2" s="11" t="s">
@@ -2959,32 +2941,32 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="16">
         <f xml:space="preserve"> SUM(G2:G6)</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>120</v>
       </c>
       <c r="E3" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="11">
         <v>0</v>
       </c>
       <c r="G3" s="11">
-        <f t="shared" ref="G3:G10" si="0" xml:space="preserve"> SUM(E3:F3)</f>
-        <v>30</v>
+        <f t="shared" ref="G3:G6" si="0" xml:space="preserve"> SUM(E3:F3)</f>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="22"/>
+      <c r="B4" s="16"/>
       <c r="D4" s="11" t="s">
         <v>122</v>
       </c>
@@ -3000,8 +2982,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="22"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="16"/>
       <c r="D5" s="11" t="s">
         <v>123</v>
       </c>
@@ -3017,10 +2999,10 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D6" s="11" t="s">
@@ -3038,23 +3020,23 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="25">
-        <v>0.89600000000000002</v>
+      <c r="B7" s="19">
+        <v>0.89500000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="24">
-        <v>0.104</v>
+      <c r="B8" s="18">
+        <v>0.105</v>
       </c>
       <c r="E8" s="5">
         <f xml:space="preserve"> SUM(E2:E6)</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" ref="F8:G8" si="1" xml:space="preserve"> SUM(F2:F6)</f>
@@ -3062,20 +3044,20 @@
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="20">
         <f xml:space="preserve"> E8/G8</f>
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="F9" s="27">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="F9" s="21">
         <f xml:space="preserve"> F8/G8</f>
-        <v>0.10416666666666667</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="G9" s="5"/>
     </row>

--- a/- Hash Values.xlsx
+++ b/- Hash Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1B3B9D-CAC9-4EA5-AE19-68D2D463705B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E5E9F2-87CD-436B-8DBD-06E6418430DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="2" r:id="rId1"/>
@@ -602,7 +602,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -633,18 +633,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -664,6 +652,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -962,12 +956,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1371,12 +1365,12 @@
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1511,12 +1505,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2106,12 +2100,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2195,7 +2189,7 @@
         <v>45</v>
       </c>
       <c r="D6" s="5" t="str">
-        <f>IF(C6=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" ref="D6:D31" si="1">IF(C6=$B$1,"Verdadeiro","Falso")</f>
         <v>Verdadeiro</v>
       </c>
       <c r="E6" s="11">
@@ -2213,7 +2207,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="5" t="str">
-        <f>IF(C7=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E7" s="11">
@@ -2231,7 +2225,7 @@
         <v>45</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f>IF(C8=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E8" s="11">
@@ -2249,7 +2243,7 @@
         <v>45</v>
       </c>
       <c r="D9" s="5" t="str">
-        <f>IF(C9=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E9" s="11">
@@ -2267,7 +2261,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="5" t="str">
-        <f>IF(C10=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E10" s="11">
@@ -2285,7 +2279,7 @@
         <v>45</v>
       </c>
       <c r="D11" s="5" t="str">
-        <f>IF(C11=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E11" s="11">
@@ -2303,7 +2297,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="5" t="str">
-        <f>IF(C12=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E12" s="11">
@@ -2321,7 +2315,7 @@
         <v>45</v>
       </c>
       <c r="D13" s="5" t="str">
-        <f>IF(C13=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E13" s="11">
@@ -2339,7 +2333,7 @@
         <v>45</v>
       </c>
       <c r="D14" s="5" t="str">
-        <f>IF(C14=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E14" s="11">
@@ -2357,7 +2351,7 @@
         <v>45</v>
       </c>
       <c r="D15" s="5" t="str">
-        <f>IF(C15=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E15" s="11">
@@ -2375,7 +2369,7 @@
         <v>45</v>
       </c>
       <c r="D16" s="5" t="str">
-        <f>IF(C16=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E16" s="11">
@@ -2393,7 +2387,7 @@
         <v>45</v>
       </c>
       <c r="D17" s="5" t="str">
-        <f>IF(C17=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E17" s="11">
@@ -2411,7 +2405,7 @@
         <v>45</v>
       </c>
       <c r="D18" s="5" t="str">
-        <f>IF(C18=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E18" s="11">
@@ -2429,7 +2423,7 @@
         <v>45</v>
       </c>
       <c r="D19" s="5" t="str">
-        <f>IF(C19=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E19" s="11">
@@ -2447,7 +2441,7 @@
         <v>45</v>
       </c>
       <c r="D20" s="5" t="str">
-        <f>IF(C20=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E20" s="11">
@@ -2465,7 +2459,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="5" t="str">
-        <f>IF(C21=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E21" s="11">
@@ -2483,7 +2477,7 @@
         <v>45</v>
       </c>
       <c r="D22" s="5" t="str">
-        <f>IF(C22=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E22" s="11">
@@ -2501,7 +2495,7 @@
         <v>45</v>
       </c>
       <c r="D23" s="5" t="str">
-        <f>IF(C23=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E23" s="11">
@@ -2519,7 +2513,7 @@
         <v>45</v>
       </c>
       <c r="D24" s="5" t="str">
-        <f>IF(C24=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E24" s="11">
@@ -2537,7 +2531,7 @@
         <v>45</v>
       </c>
       <c r="D25" s="5" t="str">
-        <f>IF(C25=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E25" s="11">
@@ -2555,7 +2549,7 @@
         <v>45</v>
       </c>
       <c r="D26" s="5" t="str">
-        <f>IF(C26=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E26" s="11">
@@ -2573,7 +2567,7 @@
         <v>45</v>
       </c>
       <c r="D27" s="5" t="str">
-        <f>IF(C27=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E27" s="11">
@@ -2591,7 +2585,7 @@
         <v>45</v>
       </c>
       <c r="D28" s="5" t="str">
-        <f>IF(C28=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E28" s="11">
@@ -2609,7 +2603,7 @@
         <v>45</v>
       </c>
       <c r="D29" s="5" t="str">
-        <f>IF(C29=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E29" s="11">
@@ -2627,7 +2621,7 @@
         <v>45</v>
       </c>
       <c r="D30" s="5" t="str">
-        <f>IF(C30=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E30" s="11">
@@ -2645,7 +2639,7 @@
         <v>45</v>
       </c>
       <c r="D31" s="5" t="str">
-        <f>IF(C31=$B$1,"Verdadeiro","Falso")</f>
+        <f t="shared" si="1"/>
         <v>Verdadeiro</v>
       </c>
       <c r="E31" s="11">
@@ -2679,12 +2673,12 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2904,10 +2898,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="5"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11" t="s">
         <v>117</v>
@@ -2920,12 +2915,13 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="13">
         <v>5</v>
       </c>
+      <c r="C2" s="5"/>
       <c r="D2" s="11" t="s">
         <v>119</v>
       </c>
@@ -2941,13 +2937,14 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <f xml:space="preserve"> SUM(G2:G6)</f>
         <v>95</v>
       </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="11" t="s">
         <v>120</v>
       </c>
@@ -2963,10 +2960,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="11" t="s">
         <v>122</v>
       </c>
@@ -2982,8 +2980,9 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="11" t="s">
         <v>123</v>
       </c>
@@ -2999,12 +2998,13 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="13" t="s">
         <v>112</v>
       </c>
+      <c r="C6" s="5"/>
       <c r="D6" s="11" t="s">
         <v>124</v>
       </c>
@@ -3020,20 +3020,27 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="24">
         <v>0.89500000000000002</v>
       </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="25">
         <v>0.105</v>
       </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="5">
         <f xml:space="preserve"> SUM(E2:E6)</f>
         <v>85</v>
@@ -3048,14 +3055,17 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="20">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="16">
         <f xml:space="preserve"> E8/G8</f>
         <v>0.89473684210526316</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="17">
         <f xml:space="preserve"> F8/G8</f>
         <v>0.10526315789473684</v>
       </c>
